--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2022.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:17</t>
+    <t xml:space="preserve">2026-09-09 21:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2022.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:01</t>
+    <t xml:space="preserve">2026-09-17 13:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2022.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:50</t>
+    <t xml:space="preserve">2026-10-05 18:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>361204.62</v>
+        <v>361204.63</v>
       </c>
     </row>
     <row r="8">
